--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7204610951008645</v>
+        <v>0.7187350263536176</v>
       </c>
       <c r="C8" t="n">
-        <v>42.69932756964457</v>
+        <v>42.74077623382846</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.25744476464938</v>
+        <v>52.22807858169622</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5763688760806917</v>
+        <v>0.574988021082894</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.633045148895293</v>
+        <v>1.629132726401533</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7187350263536176</v>
+        <v>0.7183908045977011</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74077623382846</v>
+        <v>42.72030651340996</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.22807858169622</v>
+        <v>52.25095785440613</v>
       </c>
       <c r="F8" t="n">
-        <v>0.574988021082894</v>
+        <v>0.5747126436781609</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.629132726401533</v>
+        <v>1.628352490421456</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7183908045977011</v>
+        <v>0.7204610951008645</v>
       </c>
       <c r="C8" t="n">
-        <v>42.72030651340996</v>
+        <v>42.69932756964457</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.25095785440613</v>
+        <v>52.25744476464938</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5747126436781609</v>
+        <v>0.5763688760806917</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.628352490421456</v>
+        <v>1.633045148895293</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7204610951008645</v>
+        <v>0.7180469123982767</v>
       </c>
       <c r="C8" t="n">
-        <v>42.69932756964457</v>
+        <v>42.74772618477741</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.25744476464938</v>
+        <v>52.22594542843466</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5763688760806917</v>
+        <v>0.5744375299186213</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>1.633045148895293</v>
+        <v>1.627573001436094</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7180469123982767</v>
+        <v>0.7115749525616698</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74772618477741</v>
+        <v>42.74193548387097</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.22594542843466</v>
+        <v>52.22960151802657</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5744375299186213</v>
+        <v>0.5692599620493358</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>0.4743833017077799</v>
       </c>
       <c r="H8" t="n">
-        <v>1.627573001436094</v>
+        <v>1.612903225806452</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7115749525616698</v>
+        <v>0.7075471698113208</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74193548387097</v>
+        <v>42.68867924528302</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.22960151802657</v>
+        <v>52.26415094339622</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5692599620493358</v>
+        <v>0.5660377358490566</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4743833017077799</v>
+        <v>0.4716981132075472</v>
       </c>
       <c r="H8" t="n">
-        <v>1.612903225806452</v>
+        <v>1.650943396226415</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>

--- a/aircraft/reports/manufacturer-popularity-share.xlsx
+++ b/aircraft/reports/manufacturer-popularity-share.xlsx
@@ -677,25 +677,25 @@
         <v>2025</v>
       </c>
       <c r="B8" t="n">
-        <v>0.7075471698113208</v>
+        <v>0.7022471910112359</v>
       </c>
       <c r="C8" t="n">
-        <v>42.68867924528302</v>
+        <v>42.6498127340824</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>52.26415094339622</v>
+        <v>52.29400749063671</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5660377358490566</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4716981132075472</v>
+        <v>0.4681647940074907</v>
       </c>
       <c r="H8" t="n">
-        <v>1.650943396226415</v>
+        <v>1.638576779026217</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
